--- a/data/content-review-batches/20_rows_191-200.xlsx
+++ b/data/content-review-batches/20_rows_191-200.xlsx
@@ -698,7 +698,28 @@
         <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <is>
+          <t xml:space="preserve">אופן הכנת הבצק: בקערת המיקסר שמים את הקמח, השמרים והסוכר ומערבבים.
+מוסיפים את החמאה, השמנת החמוצה והחלב ולשים כ־5 דקות.
+מוסיפים את המלח וממשיכים ללוש עוד עד לקבלת בצק חלק וגמיש (יכול לקחת גם עוד 10 דקות תלוי במיקסר)
+מעבירים לקערה, מכסים ומתפיחים במקרר למשך הלילה.
+אופן הכנת קרם השקדים: מערבבים את החמאה הרכה עם אבקת הסוכר עד לקבלת תערובת אחידה.
+מוסיפים את הביצה, תמצית הווניל והקורנפלור ומערבבים.
+לבסוף מוסיפים את אבקת השקדים ומערבבים לקרם חלק.
+הרכבה: מחלקים את הבצק לשני חלקים שווים.
+מרדדים כל חלק למלבן.
+מורחים שכבה דקה של נוטלה.
+מקפלים את הבצק לשלוש כמו שמופיע בסרטון ומרדדים שוב למלבן.
+מורחים מחצית מקרם השקדים.
+מגלגלים לרולדה או חוצים לאורך וקולעים כמו בסרטון.
+מניחים בתבניות אינגליש קייק מרופדות בנייר אפייה.
+מתפיחים עד שהרולדות כמעט מכפילות את נפחן.
+מורחים ביצה
+אופים בתנור שחומם מראש ל־170 מעלות במשך 35–45 דקות עד להזהבה.
+מי סוכר: מערבבים את הסוכר עם המים הרותחים עד שהסוכר נמס לגמרי
+מברישים את הרולדות במי הסוכר מיד כשהן יוצאות מהתנור
+בתאבון ❤️</t>
+        </is>
       </c>
       <c r="J2" t="s">
         <v>22</v>
